--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208763</v>
+        <v>121208361</v>
       </c>
       <c r="B2" t="n">
-        <v>97028</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593060</v>
+        <v>593042</v>
       </c>
       <c r="R2" t="n">
-        <v>6465162</v>
+        <v>6465133</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121208361</v>
+        <v>121205947</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593042</v>
+        <v>593207</v>
       </c>
       <c r="R3" t="n">
-        <v>6465133</v>
+        <v>6465196</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205947</v>
+        <v>121208763</v>
       </c>
       <c r="B4" t="n">
-        <v>97025</v>
+        <v>97038</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,29 +950,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593207</v>
+        <v>593060</v>
       </c>
       <c r="R4" t="n">
-        <v>6465196</v>
+        <v>6465162</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208361</v>
+        <v>121208763</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>97038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593042</v>
+        <v>593060</v>
       </c>
       <c r="R2" t="n">
-        <v>6465133</v>
+        <v>6465162</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121205947</v>
+        <v>121208361</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593207</v>
+        <v>593042</v>
       </c>
       <c r="R3" t="n">
-        <v>6465196</v>
+        <v>6465133</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121208763</v>
+        <v>121205947</v>
       </c>
       <c r="B4" t="n">
-        <v>97038</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,20 +941,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593060</v>
+        <v>593207</v>
       </c>
       <c r="R4" t="n">
-        <v>6465162</v>
+        <v>6465196</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208763</v>
+        <v>121208361</v>
       </c>
       <c r="B2" t="n">
-        <v>97038</v>
+        <v>100360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593060</v>
+        <v>593042</v>
       </c>
       <c r="R2" t="n">
-        <v>6465162</v>
+        <v>6465133</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121208361</v>
+        <v>121205947</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593042</v>
+        <v>593207</v>
       </c>
       <c r="R3" t="n">
-        <v>6465133</v>
+        <v>6465196</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205947</v>
+        <v>121208763</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>97051</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,29 +950,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593207</v>
+        <v>593060</v>
       </c>
       <c r="R4" t="n">
-        <v>6465196</v>
+        <v>6465162</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208361</v>
+        <v>121208763</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593042</v>
+        <v>593060</v>
       </c>
       <c r="R2" t="n">
-        <v>6465133</v>
+        <v>6465162</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
         <v>121205947</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121208763</v>
+        <v>121208361</v>
       </c>
       <c r="B4" t="n">
-        <v>97051</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +924,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593060</v>
+        <v>593042</v>
       </c>
       <c r="R4" t="n">
-        <v>6465162</v>
+        <v>6465133</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121208763</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121205947</v>
+        <v>121208361</v>
       </c>
       <c r="B3" t="n">
-        <v>97049</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593207</v>
+        <v>593042</v>
       </c>
       <c r="R3" t="n">
-        <v>6465196</v>
+        <v>6465133</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121208361</v>
+        <v>121205947</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593042</v>
+        <v>593207</v>
       </c>
       <c r="R4" t="n">
-        <v>6465133</v>
+        <v>6465196</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208763</v>
+        <v>121205947</v>
       </c>
       <c r="B2" t="n">
-        <v>97055</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593060</v>
+        <v>593207</v>
       </c>
       <c r="R2" t="n">
-        <v>6465162</v>
+        <v>6465196</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205947</v>
+        <v>121208763</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>97055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,29 +950,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593207</v>
+        <v>593060</v>
       </c>
       <c r="R4" t="n">
-        <v>6465196</v>
+        <v>6465162</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121205947</v>
+        <v>121208763</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +708,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593207</v>
+        <v>593060</v>
       </c>
       <c r="R2" t="n">
-        <v>6465196</v>
+        <v>6465162</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121208361</v>
+        <v>121205947</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593042</v>
+        <v>593207</v>
       </c>
       <c r="R3" t="n">
-        <v>6465133</v>
+        <v>6465196</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121208763</v>
+        <v>121208361</v>
       </c>
       <c r="B4" t="n">
-        <v>97055</v>
+        <v>100370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +924,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593060</v>
+        <v>593042</v>
       </c>
       <c r="R4" t="n">
-        <v>6465162</v>
+        <v>6465133</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121208763</v>
+        <v>121205947</v>
       </c>
       <c r="B2" t="n">
-        <v>97061</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593060</v>
+        <v>593207</v>
       </c>
       <c r="R2" t="n">
-        <v>6465162</v>
+        <v>6465196</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121205947</v>
+        <v>121208763</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>97062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,29 +829,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593207</v>
+        <v>593060</v>
       </c>
       <c r="R3" t="n">
-        <v>6465196</v>
+        <v>6465162</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
         <v>121208361</v>
       </c>
       <c r="B4" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43511-2024 artfynd.xlsx
+++ b/artfynd/A 43511-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121205947</v>
+        <v>121208361</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593207</v>
+        <v>593042</v>
       </c>
       <c r="R2" t="n">
-        <v>6465196</v>
+        <v>6465133</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121208361</v>
+        <v>121205947</v>
       </c>
       <c r="B4" t="n">
-        <v>100371</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593042</v>
+        <v>593207</v>
       </c>
       <c r="R4" t="n">
-        <v>6465133</v>
+        <v>6465196</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
